--- a/servers/maze_main_server/conf.d/data/column_relation.xlsx
+++ b/servers/maze_main_server/conf.d/data/column_relation.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10608"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF75331-E76D-A540-9B24-1FB064949993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C1FDBD-3480-1E49-9736-93F14C20B4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1700" yWindow="3020" windowWidth="21720" windowHeight="16360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="380" yWindow="1720" windowWidth="27840" windowHeight="16360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="column_relation" sheetId="2" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>外键列名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -220,6 +220,14 @@
   </si>
   <si>
     <t>primary_column</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>use_map_key_foreign</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否用map的key做外键</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -584,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.6640625" customWidth="1"/>
@@ -592,9 +600,11 @@
     <col min="3" max="3" width="18.5" customWidth="1"/>
     <col min="4" max="4" width="23.1640625" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -613,8 +623,11 @@
       <c r="F1" t="s">
         <v>16</v>
       </c>
+      <c r="G1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" ht="17">
+    <row r="2" spans="1:7" ht="17">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -633,8 +646,11 @@
       <c r="F2" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="G2" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -652,6 +668,9 @@
       </c>
       <c r="F3" s="4" t="s">
         <v>15</v>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
